--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:25:10+00:00</t>
+    <t>2023-05-05T12:31:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/documentation/ValueSet/TypeCarteVS</t>
+    <t>https://interop.esante.gouv.fr/ig/documentation/ValueSet/TypeCarteVS</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:31:03+00:00</t>
+    <t>2023-05-05T12:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/documentation/CodeSystem/type-carte-code-system</t>
+    <t>https://interop.esante.gouv.fr/ig/documentation/CodeSystem/type-carte-code-system</t>
   </si>
 </sst>
 </file>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:37:02+00:00</t>
+    <t>2023-05-05T12:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:42:02+00:00</t>
+    <t>2023-05-05T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T15:28:59+00:00</t>
+    <t>2023-05-05T15:37:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T15:37:22+00:00</t>
+    <t>2023-05-09T15:39:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:39:49+00:00</t>
+    <t>2023-05-09T15:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:41:54+00:00</t>
+    <t>2023-05-12T16:28:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TypeCarteVS.xlsx
+++ b/ig/main/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T16:28:07+00:00</t>
+    <t>2023-05-17T08:40:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
